--- a/data/chinese/P2T3_Chapter18.xlsx
+++ b/data/chinese/P2T3_Chapter18.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F48BB1-0255-B949-92D0-8BD697C47020}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB8DAE1-3566-7044-8D6D-CFB31843D3D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,118 +60,131 @@
     <t>暖和</t>
   </si>
   <si>
-    <t>溫暖、不寒冷</t>
-  </si>
-  <si>
     <t>曬過太陽的棉被摸起來十分暖和。</t>
   </si>
   <si>
     <t>激動</t>
   </si>
   <si>
-    <t>情緒興奮、起伏強烈</t>
-  </si>
-  <si>
     <t>收到期待已久的禮物，我心裡非常激動。</t>
   </si>
   <si>
     <t>水汽</t>
   </si>
   <si>
-    <t>水蒸氣遇冷形成的細小水珠霧氣</t>
-  </si>
-  <si>
     <t>熱水壺開了，瓶口不斷冒出白色水汽。</t>
   </si>
   <si>
     <t>渾身</t>
   </si>
   <si>
-    <t>整個身體、全身</t>
-  </si>
-  <si>
     <t>下雨天沒帶傘，我渾身都淋濕了。</t>
   </si>
   <si>
     <t>水淋淋</t>
   </si>
   <si>
-    <t>滿是水、濕透的樣子</t>
-  </si>
-  <si>
     <t>弟弟玩水回來，全身水淋淋的。</t>
   </si>
   <si>
     <t>越燒越旺</t>
   </si>
   <si>
-    <t>火焰持續變得猛烈</t>
-  </si>
-  <si>
     <t>不斷添加木柴，火堆就越燒越旺。</t>
   </si>
   <si>
     <t>躥出</t>
   </si>
   <si>
+    <t>火苗從柴火堆裡猛地躥出，要小心燙傷。</t>
+  </si>
+  <si>
+    <t>撲滅</t>
+  </si>
+  <si>
+    <t>發現小火苗要趕緊用水撲滅。</t>
+  </si>
+  <si>
+    <t>衝進</t>
+  </si>
+  <si>
+    <t>看見屋內冒煙，消防員立刻衝進屋救人。</t>
+  </si>
+  <si>
+    <t>變成</t>
+  </si>
+  <si>
+    <t>加熱後，冰塊會慢慢變成水。</t>
+  </si>
+  <si>
+    <t>漸漸</t>
+  </si>
+  <si>
+    <t>夕陽西下，天空的光線漸漸變暗。</t>
+  </si>
+  <si>
+    <t>嚷</t>
+  </si>
+  <si>
+    <t>弟弟找不到玩具，大聲嚷著要媽媽幫忙。</t>
+  </si>
+  <si>
+    <t>冒出</t>
+  </si>
+  <si>
+    <t>燒開水時，壺口會冒出許多白霧。</t>
+  </si>
+  <si>
+    <t>溫暖、不冷也不太熱，感覺很舒服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因為開心、興奮或緊張，心情起伏很大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水受熱後變成的小水蒸氣，比如開水冒的白煙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全身、整個身體</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身上到處都是水，濕答答的樣子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火燒得越來越大、越來越猛烈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>快速、猛地衝出來</t>
-  </si>
-  <si>
-    <t>火苗從柴火堆裡猛地躥出，要小心燙傷。</t>
-  </si>
-  <si>
-    <t>撲滅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>用拍打、覆蓋等方式熄滅火種</t>
-  </si>
-  <si>
-    <t>發現小火苗要趕緊用水撲滅。</t>
-  </si>
-  <si>
-    <t>衝進</t>
-  </si>
-  <si>
-    <t>快速用力跑進去</t>
-  </si>
-  <si>
-    <t>看見屋內冒煙，消防員立刻衝進屋救人。</t>
-  </si>
-  <si>
-    <t>變成</t>
-  </si>
-  <si>
-    <t>轉換、改換成另一種樣貌</t>
-  </si>
-  <si>
-    <t>加熱後，冰塊會慢慢變成水。</t>
-  </si>
-  <si>
-    <t>漸漸</t>
-  </si>
-  <si>
-    <t>緩慢、一點一點地</t>
-  </si>
-  <si>
-    <t>夕陽西下，天空的光線漸漸變暗。</t>
-  </si>
-  <si>
-    <t>嚷</t>
-  </si>
-  <si>
-    <t>大聲喊叫、吵鬧</t>
-  </si>
-  <si>
-    <t>弟弟找不到玩具，大聲嚷著要媽媽幫忙。</t>
-  </si>
-  <si>
-    <t>冒出</t>
-  </si>
-  <si>
-    <t>緩緩向外透出、長出</t>
-  </si>
-  <si>
-    <t>燒開水時，壺口會冒出許多白霧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很快地跑進去、闖進去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>從一種樣子變成另一種樣子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慢慢的、一點一點的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大聲喊叫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>從裡面透出來、顯露出來</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -885,10 +898,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -897,13 +910,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -912,13 +925,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -927,13 +940,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -942,13 +955,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -957,13 +970,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -972,13 +985,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -987,13 +1000,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -1002,13 +1015,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -1017,13 +1030,13 @@
     </row>
     <row r="11" spans="1:11" ht="27">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -1032,13 +1045,13 @@
     </row>
     <row r="12" spans="1:11" ht="27">
       <c r="A12" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -1047,13 +1060,13 @@
     </row>
     <row r="13" spans="1:11" ht="27">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3">
         <v>3</v>
@@ -1062,13 +1075,13 @@
     </row>
     <row r="14" spans="1:11" ht="27">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3">
         <v>3</v>
